--- a/reports/AI-Execution-Report.xlsx
+++ b/reports/AI-Execution-Report.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="84" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="91" uniqueCount="67">
   <si>
     <t>Test Case ID</t>
   </si>
@@ -47,6 +47,9 @@
   </si>
   <si>
     <t>Evidence Path</t>
+  </si>
+  <si>
+    <t>Failure Reason</t>
   </si>
   <si>
     <t>TC001</t>
@@ -78,36 +81,16 @@
     <t>High</t>
   </si>
   <si>
-    <t>Fail</t>
-  </si>
-  <si>
-    <t xml:space="preserve">ASSERTION_FAILURE: Expected URL to contain "/dashboard". Current URL: https://uat.tripcity.com/login. Visible page text: Welcome
-Email Address
-Password
-Remember Me
-LOGIN
-Need help logging in?
-New user? Sign Up for an account.
-Driver Guide
-Owner Guide
-Help Center
-Login
-Sign Up
-+1 213 292 5663
-support@tripcity.com
-REPORT AN ACCIDENT: +1 213 513 2953 · claims@tripcity.com
-Copyright © 2026 TripCity. All Rights Reserved.
-×
-!
-Warning
-The email or password you entered is incorrect.
-OK. Navigation error: page.waitForURL: Timeout 8000ms exceeded.
-=========================== logs ===========================
-waiting for navigation until "load"
-============================================================</t>
-  </si>
-  <si>
-    <t>evidence\TC001-failure.png</t>
+    <t>PASS</t>
+  </si>
+  <si>
+    <t>All planned actions and verification assertions completed.</t>
+  </si>
+  <si>
+    <t>evidence\TC001.png</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>TC002</t>
@@ -133,13 +116,10 @@
     <t>Login is prevented and an error message is displayed</t>
   </si>
   <si>
-    <t>Pass</t>
-  </si>
-  <si>
-    <t>All planned actions and verification assertions completed.</t>
-  </si>
-  <si>
-    <t>evidence\TC002.png</t>
+    <t>BLOCKED</t>
+  </si>
+  <si>
+    <t>AUTOMATION_BLOCKED: Password fields must use the {{TEST_PASSWORD}} placeholder.</t>
   </si>
   <si>
     <t>TC003</t>
@@ -168,13 +148,13 @@
     <t>Login is prevented and a validation error for the mandatory email field is displayed</t>
   </si>
   <si>
-    <t>Blocked</t>
-  </si>
-  <si>
-    <t>AUTOMATION_BLOCKED: AI did not provide an executable plan.</t>
-  </si>
-  <si>
-    <t/>
+    <t>FAIL</t>
+  </si>
+  <si>
+    <t>ASSERTION_FAILURE: Expected element to become visible: Email field is mandatory within 8000ms.</t>
+  </si>
+  <si>
+    <t>evidence\TC003-failure.png</t>
   </si>
   <si>
     <t>TC004</t>
@@ -197,6 +177,12 @@
     <t>Login is prevented and a validation error for the mandatory password field is displayed</t>
   </si>
   <si>
+    <t>ASSERTION_FAILURE: Expected element to become visible: Password field is mandatory within 8000ms.</t>
+  </si>
+  <si>
+    <t>evidence\TC004-failure.png</t>
+  </si>
+  <si>
     <t>TC005</t>
   </si>
   <si>
@@ -220,13 +206,7 @@
     <t>Medium</t>
   </si>
   <si>
-    <t xml:space="preserve">AUTOMATION_BLOCKED: Unable to fill "#signin_email_address". Current URL: https://uat.tripcity.com/signin. locator.waitFor: Timeout 8000ms exceeded.
-Call log:
-[2m  - waiting for locator('#signin_email_address') to be visible[22m
-</t>
-  </si>
-  <si>
-    <t>evidence\TC005-failure.png</t>
+    <t>AUTOMATION_BLOCKED: Username fields must use the {{TEST_USERNAME}} placeholder.</t>
   </si>
   <si>
     <t>TC006</t>
@@ -241,33 +221,7 @@
     <t>User is successfully navigated to the dashboard</t>
   </si>
   <si>
-    <t xml:space="preserve">ASSERTION_FAILURE: Expected URL to contain "dashboard". Current URL: https://uat.tripcity.com/login. Visible page text: Welcome
-Email Address
-Password
-Remember Me
-LOGIN
-Need help logging in?
-New user? Sign Up for an account.
-Driver Guide
-Owner Guide
-Help Center
-Login
-Sign Up
-+1 213 292 5663
-support@tripcity.com
-REPORT AN ACCIDENT: +1 213 513 2953 · claims@tripcity.com
-Copyright © 2026 TripCity. All Rights Reserved.
-×
-!
-Warning
-The email or password you entered is incorrect.
-OK. Navigation error: page.waitForURL: Timeout 8000ms exceeded.
-=========================== logs ===========================
-waiting for navigation until "load"
-============================================================</t>
-  </si>
-  <si>
-    <t>evidence\TC006-failure.png</t>
+    <t>evidence\TC006.png</t>
   </si>
 </sst>
 </file>
@@ -650,7 +604,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L7"/>
+  <dimension ref="A1:M7"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="15" customWidth="1"/>
@@ -663,9 +617,10 @@
     <col min="9" max="9" width="12" customWidth="1"/>
     <col min="10" max="10" width="18" customWidth="1"/>
     <col min="11" max="12" width="35" customWidth="1"/>
+    <col min="13" max="13" width="55" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="1" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" s="1" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -702,237 +657,258 @@
       <c r="L1" s="1" t="s">
         <v>11</v>
       </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="B2" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="C2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="D2" t="s">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="E2" t="s">
+        <v>17</v>
+      </c>
+      <c r="F2" t="s">
+        <v>18</v>
+      </c>
+      <c r="G2" t="s">
+        <v>19</v>
+      </c>
+      <c r="H2" t="s">
+        <v>20</v>
+      </c>
+      <c r="I2" t="s">
+        <v>21</v>
+      </c>
+      <c r="J2" t="s">
+        <v>22</v>
+      </c>
+      <c r="K2" t="s">
+        <v>23</v>
+      </c>
+      <c r="L2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M2" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A3" t="s">
+        <v>26</v>
+      </c>
+      <c r="B3" t="s">
+        <v>27</v>
+      </c>
+      <c r="C3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D3" t="s">
+        <v>29</v>
+      </c>
+      <c r="E3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F3" t="s">
+        <v>30</v>
+      </c>
+      <c r="G3" t="s">
+        <v>31</v>
+      </c>
+      <c r="H3" t="s">
+        <v>32</v>
+      </c>
+      <c r="I3" t="s">
+        <v>21</v>
+      </c>
+      <c r="J3" t="s">
+        <v>33</v>
+      </c>
+      <c r="K3" t="s">
+        <v>34</v>
+      </c>
+      <c r="L3" t="s">
+        <v>25</v>
+      </c>
+      <c r="M3" t="s">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A4" t="s">
+        <v>35</v>
+      </c>
+      <c r="B4" t="s">
+        <v>36</v>
+      </c>
+      <c r="C4" t="s">
+        <v>37</v>
+      </c>
+      <c r="D4" t="s">
+        <v>38</v>
+      </c>
+      <c r="E4" t="s">
+        <v>39</v>
+      </c>
+      <c r="F4" t="s">
+        <v>40</v>
+      </c>
+      <c r="G4" t="s">
+        <v>41</v>
+      </c>
+      <c r="H4" t="s">
+        <v>42</v>
+      </c>
+      <c r="I4" t="s">
+        <v>21</v>
+      </c>
+      <c r="J4" t="s">
+        <v>43</v>
+      </c>
+      <c r="K4" t="s">
+        <v>44</v>
+      </c>
+      <c r="L4" t="s">
+        <v>45</v>
+      </c>
+      <c r="M4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A5" t="s">
+        <v>46</v>
+      </c>
+      <c r="B5" t="s">
+        <v>47</v>
+      </c>
+      <c r="C5" t="s">
+        <v>48</v>
+      </c>
+      <c r="D5" t="s">
+        <v>38</v>
+      </c>
+      <c r="E5" t="s">
+        <v>39</v>
+      </c>
+      <c r="F5" t="s">
+        <v>49</v>
+      </c>
+      <c r="G5" t="s">
+        <v>50</v>
+      </c>
+      <c r="H5" t="s">
+        <v>51</v>
+      </c>
+      <c r="I5" t="s">
+        <v>21</v>
+      </c>
+      <c r="J5" t="s">
+        <v>43</v>
+      </c>
+      <c r="K5" t="s">
+        <v>52</v>
+      </c>
+      <c r="L5" t="s">
+        <v>53</v>
+      </c>
+      <c r="M5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A6" t="s">
+        <v>54</v>
+      </c>
+      <c r="B6" t="s">
+        <v>55</v>
+      </c>
+      <c r="C6" t="s">
+        <v>56</v>
+      </c>
+      <c r="D6" t="s">
+        <v>38</v>
+      </c>
+      <c r="E6" t="s">
+        <v>39</v>
+      </c>
+      <c r="F6" t="s">
+        <v>57</v>
+      </c>
+      <c r="G6" t="s">
+        <v>58</v>
+      </c>
+      <c r="H6" t="s">
+        <v>59</v>
+      </c>
+      <c r="I6" t="s">
+        <v>60</v>
+      </c>
+      <c r="J6" t="s">
+        <v>33</v>
+      </c>
+      <c r="K6" t="s">
+        <v>61</v>
+      </c>
+      <c r="L6" t="s">
+        <v>25</v>
+      </c>
+      <c r="M6" t="s">
+        <v>61</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A7" t="s">
+        <v>62</v>
+      </c>
+      <c r="B7" t="s">
+        <v>63</v>
+      </c>
+      <c r="C7" t="s">
+        <v>64</v>
+      </c>
+      <c r="D7" t="s">
         <v>16</v>
       </c>
-      <c r="F2" t="s">
+      <c r="E7" t="s">
         <v>17</v>
       </c>
-      <c r="G2" t="s">
+      <c r="F7" t="s">
         <v>18</v>
       </c>
-      <c r="H2" t="s">
+      <c r="G7" t="s">
         <v>19</v>
       </c>
-      <c r="I2" t="s">
-        <v>20</v>
-      </c>
-      <c r="J2" t="s">
+      <c r="H7" t="s">
+        <v>65</v>
+      </c>
+      <c r="I7" t="s">
         <v>21</v>
       </c>
-      <c r="K2" t="s">
+      <c r="J7" t="s">
         <v>22</v>
       </c>
-      <c r="L2" t="s">
+      <c r="K7" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>24</v>
-      </c>
-      <c r="B3" t="s">
+      <c r="L7" t="s">
+        <v>66</v>
+      </c>
+      <c r="M7" t="s">
         <v>25</v>
-      </c>
-      <c r="C3" t="s">
-        <v>26</v>
-      </c>
-      <c r="D3" t="s">
-        <v>27</v>
-      </c>
-      <c r="E3" t="s">
-        <v>16</v>
-      </c>
-      <c r="F3" t="s">
-        <v>28</v>
-      </c>
-      <c r="G3" t="s">
-        <v>29</v>
-      </c>
-      <c r="H3" t="s">
-        <v>30</v>
-      </c>
-      <c r="I3" t="s">
-        <v>20</v>
-      </c>
-      <c r="J3" t="s">
-        <v>31</v>
-      </c>
-      <c r="K3" t="s">
-        <v>32</v>
-      </c>
-      <c r="L3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>34</v>
-      </c>
-      <c r="B4" t="s">
-        <v>35</v>
-      </c>
-      <c r="C4" t="s">
-        <v>36</v>
-      </c>
-      <c r="D4" t="s">
-        <v>37</v>
-      </c>
-      <c r="E4" t="s">
-        <v>38</v>
-      </c>
-      <c r="F4" t="s">
-        <v>39</v>
-      </c>
-      <c r="G4" t="s">
-        <v>40</v>
-      </c>
-      <c r="H4" t="s">
-        <v>41</v>
-      </c>
-      <c r="I4" t="s">
-        <v>20</v>
-      </c>
-      <c r="J4" t="s">
-        <v>42</v>
-      </c>
-      <c r="K4" t="s">
-        <v>43</v>
-      </c>
-      <c r="L4" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>45</v>
-      </c>
-      <c r="B5" t="s">
-        <v>46</v>
-      </c>
-      <c r="C5" t="s">
-        <v>47</v>
-      </c>
-      <c r="D5" t="s">
-        <v>37</v>
-      </c>
-      <c r="E5" t="s">
-        <v>38</v>
-      </c>
-      <c r="F5" t="s">
-        <v>48</v>
-      </c>
-      <c r="G5" t="s">
-        <v>49</v>
-      </c>
-      <c r="H5" t="s">
-        <v>50</v>
-      </c>
-      <c r="I5" t="s">
-        <v>20</v>
-      </c>
-      <c r="J5" t="s">
-        <v>42</v>
-      </c>
-      <c r="K5" t="s">
-        <v>43</v>
-      </c>
-      <c r="L5" t="s">
-        <v>44</v>
-      </c>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>51</v>
-      </c>
-      <c r="B6" t="s">
-        <v>52</v>
-      </c>
-      <c r="C6" t="s">
-        <v>53</v>
-      </c>
-      <c r="D6" t="s">
-        <v>37</v>
-      </c>
-      <c r="E6" t="s">
-        <v>38</v>
-      </c>
-      <c r="F6" t="s">
-        <v>54</v>
-      </c>
-      <c r="G6" t="s">
-        <v>55</v>
-      </c>
-      <c r="H6" t="s">
-        <v>56</v>
-      </c>
-      <c r="I6" t="s">
-        <v>57</v>
-      </c>
-      <c r="J6" t="s">
-        <v>42</v>
-      </c>
-      <c r="K6" t="s">
-        <v>58</v>
-      </c>
-      <c r="L6" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>60</v>
-      </c>
-      <c r="B7" t="s">
-        <v>61</v>
-      </c>
-      <c r="C7" t="s">
-        <v>62</v>
-      </c>
-      <c r="D7" t="s">
-        <v>15</v>
-      </c>
-      <c r="E7" t="s">
-        <v>16</v>
-      </c>
-      <c r="F7" t="s">
-        <v>17</v>
-      </c>
-      <c r="G7" t="s">
-        <v>18</v>
-      </c>
-      <c r="H7" t="s">
-        <v>63</v>
-      </c>
-      <c r="I7" t="s">
-        <v>20</v>
-      </c>
-      <c r="J7" t="s">
-        <v>21</v>
-      </c>
-      <c r="K7" t="s">
-        <v>64</v>
-      </c>
-      <c r="L7" t="s">
-        <v>65</v>
       </c>
     </row>
   </sheetData>
-  <autoFilter ref="A1:L7"/>
+  <autoFilter ref="A1:M7"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1" firstPageNumber="1" useFirstPageNumber="1" copies="1"/>
 </worksheet>
